--- a/feedback_surveys/023_youth_climate_policy_understanding_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/023_youth_climate_policy_understanding_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>climate_change_introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -528,7 +528,11 @@
           <t>Introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This is the introduction to the survey</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,30 +542,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>climate_change</t>
+          <t>climate_changeawareness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>climate_change</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Climate Change Awareness</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How aware are you of climate change?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>climate_policies</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Climate Policies</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>What are your opinions on climate policies?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>policy_awareness</t>
+          <t>policy_ideas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>policy_awareness</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Policy Ideas</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Do you have any ideas for climate policies?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,23 +623,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>policy_attitudes</t>
+          <t>demographic_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>policy_attitudes</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Demographic Information</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide your demographic information</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +655,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>policy_ideas</t>
+          <t>age_range</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>policy_ideas</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Age Range</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What is your age range?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>demographic_info</t>
+          <t>education_level</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>demographic_info</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Education Level</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What is your education level?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,41 +709,49 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>age_range</t>
+          <t>region_range</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>age_range</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Which region do you live in?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>gender_range</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gender_range</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>What language do you prefer to communicate?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +763,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>education_level</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>education_level</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Contact Number</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide your contact number</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>income_range</t>
+          <t>submission</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>income_range</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Submission</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please submit your feedback</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>region_range</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>region_range</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Do you have any comments or feedback?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>other_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>language</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Other Comments</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Do you have any other comments or feedback?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -824,220 +876,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide your email</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>other_comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>other_comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1052,12 +901,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1080,153 +929,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>climate_policies_choices</t>
+          <t>climate_changeawareness_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>climate_policies_choices</t>
+          <t>climate_changeawareness_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>climate_policies_choices</t>
+          <t>climate_changeawareness_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>policy_awareness_choices</t>
+          <t>climate_policies_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>policy_awareness_choices</t>
+          <t>climate_policies_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>policy_awareness_choices</t>
+          <t>climate_policies_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>policy_attitudes_choices</t>
+          <t>climate_policies_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>policy_attitudes_choices</t>
+          <t>climate_policies_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>policy_attitudes_choices</t>
+          <t>demographic_info_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1087,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1255,165 +1104,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>demographic_info_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_range_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>gender_range_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>gender_range_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'label':_'option_3'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>submission_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
